--- a/data/dividends_info_20261005.xlsx
+++ b/data/dividends_info_20261005.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50.84000015258789</v>
+        <v>50.86999893188477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1770259632767109</v>
+        <v>0.1769215684877653</v>
       </c>
       <c r="J2" t="n">
         <v>161</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>61.70000076293945</v>
+        <v>61.54999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.134521866036118</v>
+        <v>1.13728677282991</v>
       </c>
       <c r="J3" t="n">
         <v>140</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.899999618530273</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="I4" t="n">
-        <v>0.674157332266361</v>
+        <v>0.6696428542918696</v>
       </c>
       <c r="J4" t="n">
         <v>70</v>
@@ -710,12 +710,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>50.81999969482422</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.1770956327045513</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>70</v>
       </c>
@@ -758,10 +754,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.025000095367432</v>
+        <v>2.029999971389771</v>
       </c>
       <c r="I7" t="n">
-        <v>3.802468956725087</v>
+        <v>3.79310350173476</v>
       </c>
       <c r="J7" t="n">
         <v>49</v>
@@ -805,10 +801,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>49.63999938964844</v>
+        <v>49.65999984741211</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6661966238238145</v>
+        <v>0.6659283145713371</v>
       </c>
       <c r="J8" t="n">
         <v>49</v>
@@ -852,10 +848,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.3700008392334</v>
+        <v>24.40999984741211</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1079195350922</v>
+        <v>1.106104062629172</v>
       </c>
       <c r="J9" t="n">
         <v>49</v>
@@ -899,10 +895,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26.02000045776367</v>
+        <v>26.04000091552734</v>
       </c>
       <c r="I10" t="n">
-        <v>2.267486508917258</v>
+        <v>2.265744928020298</v>
       </c>
       <c r="J10" t="n">
         <v>49</v>
@@ -946,10 +942,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11.69999980926514</v>
+        <v>11.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.79487182413202</v>
+        <v>1.826086956521739</v>
       </c>
       <c r="J11" t="n">
         <v>42</v>
@@ -993,10 +989,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.940000057220459</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I12" t="n">
-        <v>3.367003334568775</v>
+        <v>3.36134464556733</v>
       </c>
       <c r="J12" t="n">
         <v>42</v>
@@ -1087,10 +1083,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.460000038146973</v>
+        <v>8.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7092198549580861</v>
+        <v>0.7058823529411764</v>
       </c>
       <c r="J14" t="n">
         <v>35</v>
@@ -1134,10 +1130,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.52999973297119</v>
+        <v>10.5</v>
       </c>
       <c r="I15" t="n">
-        <v>4.368471145917155</v>
+        <v>4.380952380952381</v>
       </c>
       <c r="J15" t="n">
         <v>21</v>
@@ -1275,10 +1271,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.949999809265137</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="I18" t="n">
-        <v>1.010101049022522</v>
+        <v>1.072961408523802</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1322,10 +1318,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7.980000019073486</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4761904750523042</v>
+        <v>0.475</v>
       </c>
       <c r="J19" t="n">
         <v>-7</v>
@@ -1368,12 +1364,8 @@
           <t>IT0003132476</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>24.3700008392334</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.1079195350922</v>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>-14</v>
       </c>
@@ -1416,10 +1408,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.901000022888184</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="I21" t="n">
-        <v>2.998421847118133</v>
+        <v>3.00000003764504</v>
       </c>
       <c r="J21" t="n">
         <v>-14</v>
@@ -1462,12 +1454,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>50.81999969482422</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.1770956327045513</v>
-      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>-14</v>
       </c>
@@ -1510,10 +1498,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>93</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="I23" t="n">
-        <v>1.43010752688172</v>
+        <v>1.423221020260309</v>
       </c>
       <c r="J23" t="n">
         <v>-14</v>
@@ -1557,10 +1545,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.039999961853027</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="I24" t="n">
-        <v>4.966887448588033</v>
+        <v>4.950495096249109</v>
       </c>
       <c r="J24" t="n">
         <v>-21</v>
@@ -3422,7 +3410,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3439,7 +3427,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3456,7 +3444,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3466,14 +3454,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3483,14 +3471,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3507,7 +3495,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3524,7 +3512,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3534,14 +3522,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3551,14 +3539,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3568,14 +3556,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3585,7 +3573,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3631,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3660,7 +3648,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3677,7 +3665,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3715,299 +3703,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Anima Holding S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ariston Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ariston Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Bper Banca S.P.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CELLULARLINE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CELLULARLINE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FinecoBank S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Nexi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TELECOM ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>